--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122915193</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,637 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123311089</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>524298</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6713774</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123311251</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>524319</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6713759</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123310872</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>524248</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6713835</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123311851</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>524449</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6713483</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123311027</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>524271</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6713818</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1440,6 +1440,258 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123359713</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>524277</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6713805</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123360098</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>524214</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6713889</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1692,142 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123411453</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524217</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6713890</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>10-20 bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122915193</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311089</v>
+        <v>123310872</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -859,21 +859,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524298</v>
+        <v>524248</v>
       </c>
       <c r="R3" t="n">
-        <v>6713774</v>
+        <v>6713835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -915,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123311251</v>
+        <v>123311089</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1001,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524319</v>
+        <v>524298</v>
       </c>
       <c r="R4" t="n">
-        <v>6713759</v>
+        <v>6713774</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1046,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123310872</v>
+        <v>123311251</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,12 +1103,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1121,16 +1116,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524248</v>
+        <v>524319</v>
       </c>
       <c r="R5" t="n">
-        <v>6713835</v>
+        <v>6713759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1202,7 +1202,7 @@
         <v>123311851</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>123311027</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>123359713</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>123360098</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122915193</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123310872</v>
+        <v>123311089</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -859,16 +859,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524248</v>
+        <v>524298</v>
       </c>
       <c r="R3" t="n">
-        <v>6713835</v>
+        <v>6713774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +905,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +915,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123311089</v>
+        <v>123311851</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,57 +954,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524298</v>
+        <v>524449</v>
       </c>
       <c r="R4" t="n">
-        <v>6713774</v>
+        <v>6713483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123311251</v>
+        <v>123310872</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,12 +1089,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1116,21 +1102,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524319</v>
+        <v>524248</v>
       </c>
       <c r="R5" t="n">
-        <v>6713759</v>
+        <v>6713835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311851</v>
+        <v>123311251</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,38 +1192,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524449</v>
+        <v>524319</v>
       </c>
       <c r="R6" t="n">
-        <v>6713483</v>
+        <v>6713759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
         <v>123311027</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123359713</v>
+        <v>123360098</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524277</v>
+        <v>524214</v>
       </c>
       <c r="R8" t="n">
-        <v>6713805</v>
+        <v>6713889</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123360098</v>
+        <v>123359713</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524214</v>
+        <v>524277</v>
       </c>
       <c r="R9" t="n">
-        <v>6713889</v>
+        <v>6713805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,7 +1697,7 @@
         <v>123411453</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122915193</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311089</v>
+        <v>123310872</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -859,21 +859,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524298</v>
+        <v>524248</v>
       </c>
       <c r="R3" t="n">
-        <v>6713774</v>
+        <v>6713835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -915,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,7 +940,7 @@
         <v>123311851</v>
       </c>
       <c r="B4" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1054,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123310872</v>
+        <v>123311251</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1089,12 +1084,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1102,16 +1097,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524248</v>
+        <v>524319</v>
       </c>
       <c r="R5" t="n">
-        <v>6713835</v>
+        <v>6713759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311251</v>
+        <v>123311089</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524319</v>
+        <v>524298</v>
       </c>
       <c r="R6" t="n">
-        <v>6713759</v>
+        <v>6713774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
         <v>123311027</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>123360098</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>123359713</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>123411453</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1827,6 +1827,1358 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123524383</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524223</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6713905</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123524565</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>524196</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6713921</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123526406</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>524109</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6713892</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123523873</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>524302</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6713791</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123524367</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>524214</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6713917</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123526941</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>524150</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6713800</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123525488</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>524128</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6714020</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123524063</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>524262</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6713854</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123524517</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>524209</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6713935</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123526961</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>524165</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6713796</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123524950</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>524192</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6713963</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122915193</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311251</v>
+        <v>123311851</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,57 +823,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524319</v>
+        <v>524449</v>
       </c>
       <c r="R3" t="n">
-        <v>6713759</v>
+        <v>6713483</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -915,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,7 +926,7 @@
         <v>123311027</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1073,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123311089</v>
+        <v>123310872</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,12 +1089,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1121,21 +1102,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524298</v>
+        <v>524248</v>
       </c>
       <c r="R5" t="n">
-        <v>6713774</v>
+        <v>6713835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1167,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311851</v>
+        <v>123311089</v>
       </c>
       <c r="B6" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,38 +1192,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524449</v>
+        <v>524298</v>
       </c>
       <c r="R6" t="n">
-        <v>6713483</v>
+        <v>6713774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123310872</v>
+        <v>123311251</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,12 +1346,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1364,16 +1359,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524248</v>
+        <v>524319</v>
       </c>
       <c r="R7" t="n">
-        <v>6713835</v>
+        <v>6713759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,7 +1445,7 @@
         <v>123360098</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>123359713</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>123411453</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123524950</v>
+        <v>123526406</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,43 +1842,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524192</v>
+        <v>524109</v>
       </c>
       <c r="R11" t="n">
-        <v>6713963</v>
+        <v>6713892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,7 +1924,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1920,7 +1934,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,7 +1969,7 @@
         <v>123524383</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2073,10 +2092,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524517</v>
+        <v>123525488</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,38 +2104,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524209</v>
+        <v>524128</v>
       </c>
       <c r="R13" t="n">
-        <v>6713935</v>
+        <v>6714020</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2158,7 +2196,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2185,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524367</v>
+        <v>123526961</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2197,52 +2240,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524214</v>
+        <v>524165</v>
       </c>
       <c r="R14" t="n">
-        <v>6713917</v>
+        <v>6713796</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2274,7 +2308,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2284,7 +2318,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2311,10 +2345,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524565</v>
+        <v>123526941</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2352,14 +2386,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524196</v>
+        <v>524150</v>
       </c>
       <c r="R15" t="n">
-        <v>6713921</v>
+        <v>6713800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2391,7 +2425,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2401,7 +2435,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2428,10 +2462,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123523873</v>
+        <v>123524950</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2440,57 +2474,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524302</v>
+        <v>524192</v>
       </c>
       <c r="R16" t="n">
-        <v>6713791</v>
+        <v>6713963</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2522,7 +2542,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2532,12 +2552,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2564,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123526961</v>
+        <v>123524565</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2609,10 +2624,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524165</v>
+        <v>524196</v>
       </c>
       <c r="R17" t="n">
-        <v>6713796</v>
+        <v>6713921</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2644,7 +2659,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2654,7 +2669,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2681,10 +2696,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123526941</v>
+        <v>123524517</v>
       </c>
       <c r="B18" t="n">
-        <v>57497</v>
+        <v>8445</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2693,43 +2708,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524150</v>
+        <v>524209</v>
       </c>
       <c r="R18" t="n">
-        <v>6713800</v>
+        <v>6713935</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2761,7 +2771,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2771,7 +2781,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2798,10 +2808,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123525488</v>
+        <v>123524063</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>8445</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2810,57 +2820,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524128</v>
+        <v>524262</v>
       </c>
       <c r="R19" t="n">
-        <v>6714020</v>
+        <v>6713854</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2892,7 +2883,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2902,12 +2893,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2934,10 +2920,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123524063</v>
+        <v>123523873</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2946,38 +2932,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524262</v>
+        <v>524302</v>
       </c>
       <c r="R20" t="n">
-        <v>6713854</v>
+        <v>6713791</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3009,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3019,7 +3024,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3046,10 +3056,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123526406</v>
+        <v>123524367</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3081,12 +3091,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3094,21 +3104,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524109</v>
+        <v>524214</v>
       </c>
       <c r="R21" t="n">
-        <v>6713892</v>
+        <v>6713917</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3140,7 +3145,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3150,12 +3155,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311851</v>
+        <v>123311251</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +823,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524449</v>
+        <v>524319</v>
       </c>
       <c r="R3" t="n">
-        <v>6713483</v>
+        <v>6713759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +905,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +915,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123311027</v>
+        <v>123310872</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,12 +977,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -971,21 +990,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524271</v>
+        <v>524248</v>
       </c>
       <c r="R4" t="n">
-        <v>6713818</v>
+        <v>6713835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123310872</v>
+        <v>123311851</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,52 +1080,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524248</v>
+        <v>524449</v>
       </c>
       <c r="R5" t="n">
-        <v>6713835</v>
+        <v>6713483</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,7 +1183,7 @@
         <v>123311089</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123311251</v>
+        <v>123311027</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524319</v>
+        <v>524271</v>
       </c>
       <c r="R7" t="n">
-        <v>6713759</v>
+        <v>6713818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123360098</v>
+        <v>123359713</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524214</v>
+        <v>524277</v>
       </c>
       <c r="R8" t="n">
-        <v>6713889</v>
+        <v>6713805</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123359713</v>
+        <v>123360098</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524277</v>
+        <v>524214</v>
       </c>
       <c r="R9" t="n">
-        <v>6713805</v>
+        <v>6713889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,7 +1697,7 @@
         <v>123411453</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123526406</v>
+        <v>123525488</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524109</v>
+        <v>524128</v>
       </c>
       <c r="R11" t="n">
-        <v>6713892</v>
+        <v>6714020</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,10 +1966,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524383</v>
+        <v>123526961</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,52 +1978,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524223</v>
+        <v>524165</v>
       </c>
       <c r="R12" t="n">
-        <v>6713905</v>
+        <v>6713796</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2055,7 +2046,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2065,7 +2056,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2092,10 +2083,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123525488</v>
+        <v>123523873</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2127,12 +2118,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2151,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524128</v>
+        <v>524302</v>
       </c>
       <c r="R13" t="n">
-        <v>6714020</v>
+        <v>6713791</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2186,7 +2177,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2196,12 +2187,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2228,10 +2219,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123526961</v>
+        <v>123526406</v>
       </c>
       <c r="B14" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2240,43 +2231,57 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524165</v>
+        <v>524109</v>
       </c>
       <c r="R14" t="n">
-        <v>6713796</v>
+        <v>6713892</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2308,7 +2313,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2318,7 +2323,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2345,10 +2355,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123526941</v>
+        <v>123524565</v>
       </c>
       <c r="B15" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2386,14 +2396,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524150</v>
+        <v>524196</v>
       </c>
       <c r="R15" t="n">
-        <v>6713800</v>
+        <v>6713921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2425,7 +2435,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2435,7 +2445,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2462,10 +2472,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123524950</v>
+        <v>123524517</v>
       </c>
       <c r="B16" t="n">
-        <v>57503</v>
+        <v>8447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2474,43 +2484,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524192</v>
+        <v>524209</v>
       </c>
       <c r="R16" t="n">
-        <v>6713963</v>
+        <v>6713935</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2542,7 +2547,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2552,7 +2557,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,10 +2584,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123524565</v>
+        <v>123526941</v>
       </c>
       <c r="B17" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2620,14 +2625,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524196</v>
+        <v>524150</v>
       </c>
       <c r="R17" t="n">
-        <v>6713921</v>
+        <v>6713800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2659,7 +2664,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2669,7 +2674,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2696,10 +2701,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123524517</v>
+        <v>123524383</v>
       </c>
       <c r="B18" t="n">
-        <v>8445</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2708,38 +2713,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524209</v>
+        <v>524223</v>
       </c>
       <c r="R18" t="n">
-        <v>6713935</v>
+        <v>6713905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2771,7 +2790,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2781,7 +2800,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2808,10 +2827,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123524063</v>
+        <v>123524950</v>
       </c>
       <c r="B19" t="n">
-        <v>8445</v>
+        <v>57506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2820,38 +2839,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524262</v>
+        <v>524192</v>
       </c>
       <c r="R19" t="n">
-        <v>6713854</v>
+        <v>6713963</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2883,7 +2907,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2893,7 +2917,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2920,10 +2944,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123523873</v>
+        <v>123524367</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2955,7 +2979,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2968,21 +2992,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524302</v>
+        <v>524214</v>
       </c>
       <c r="R20" t="n">
-        <v>6713791</v>
+        <v>6713917</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3014,7 +3033,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,12 +3043,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3056,10 +3070,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123524367</v>
+        <v>123524063</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3068,52 +3082,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524214</v>
+        <v>524262</v>
       </c>
       <c r="R21" t="n">
-        <v>6713917</v>
+        <v>6713854</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311251</v>
+        <v>123310872</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -859,21 +859,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524319</v>
+        <v>524248</v>
       </c>
       <c r="R3" t="n">
-        <v>6713759</v>
+        <v>6713835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -915,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123310872</v>
+        <v>123311851</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,52 +949,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524248</v>
+        <v>524449</v>
       </c>
       <c r="R4" t="n">
-        <v>6713835</v>
+        <v>6713483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123311851</v>
+        <v>123311251</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,38 +1061,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524449</v>
+        <v>524319</v>
       </c>
       <c r="R5" t="n">
-        <v>6713483</v>
+        <v>6713759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311089</v>
+        <v>123311027</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524298</v>
+        <v>524271</v>
       </c>
       <c r="R6" t="n">
-        <v>6713774</v>
+        <v>6713818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123311027</v>
+        <v>123311089</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524271</v>
+        <v>524298</v>
       </c>
       <c r="R7" t="n">
-        <v>6713818</v>
+        <v>6713774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,7 +1445,7 @@
         <v>123359713</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>123360098</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>123411453</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123525488</v>
+        <v>123524565</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,57 +1842,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524128</v>
+        <v>524196</v>
       </c>
       <c r="R11" t="n">
-        <v>6714020</v>
+        <v>6713921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1910,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1934,12 +1920,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,10 +1947,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123526961</v>
+        <v>123523873</v>
       </c>
       <c r="B12" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,43 +1959,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524165</v>
+        <v>524302</v>
       </c>
       <c r="R12" t="n">
-        <v>6713796</v>
+        <v>6713791</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2046,7 +2041,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2056,7 +2051,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123523873</v>
+        <v>123524367</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2131,21 +2131,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524302</v>
+        <v>524214</v>
       </c>
       <c r="R13" t="n">
-        <v>6713791</v>
+        <v>6713917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2177,7 +2172,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2187,12 +2182,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2219,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123526406</v>
+        <v>123526941</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2231,45 +2221,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2278,10 +2254,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524109</v>
+        <v>524150</v>
       </c>
       <c r="R14" t="n">
-        <v>6713892</v>
+        <v>6713800</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2313,7 +2289,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2323,12 +2299,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2355,10 +2326,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524565</v>
+        <v>123524063</v>
       </c>
       <c r="B15" t="n">
-        <v>57506</v>
+        <v>8447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2367,43 +2338,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524196</v>
+        <v>524262</v>
       </c>
       <c r="R15" t="n">
-        <v>6713921</v>
+        <v>6713854</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2435,7 +2401,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2445,7 +2411,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2584,10 +2550,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123526941</v>
+        <v>123526406</v>
       </c>
       <c r="B17" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2596,31 +2562,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2629,10 +2609,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524150</v>
+        <v>524109</v>
       </c>
       <c r="R17" t="n">
-        <v>6713800</v>
+        <v>6713892</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2664,7 +2644,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2674,7 +2654,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2704,7 +2689,7 @@
         <v>123524383</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2827,10 +2812,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123524950</v>
+        <v>123525488</v>
       </c>
       <c r="B19" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2839,43 +2824,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524192</v>
+        <v>524128</v>
       </c>
       <c r="R19" t="n">
-        <v>6713963</v>
+        <v>6714020</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2907,7 +2906,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2917,7 +2916,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2944,10 +2948,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123524367</v>
+        <v>123524950</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2956,52 +2960,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524214</v>
+        <v>524192</v>
       </c>
       <c r="R20" t="n">
-        <v>6713917</v>
+        <v>6713963</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3033,7 +3028,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3043,7 +3038,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3070,10 +3065,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123524063</v>
+        <v>123526961</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3082,38 +3077,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524262</v>
+        <v>524165</v>
       </c>
       <c r="R21" t="n">
-        <v>6713854</v>
+        <v>6713796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -2083,10 +2083,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524367</v>
+        <v>123526941</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2095,40 +2095,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2137,10 +2128,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524214</v>
+        <v>524150</v>
       </c>
       <c r="R13" t="n">
-        <v>6713917</v>
+        <v>6713800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2163,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2182,7 +2173,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2209,10 +2200,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123526941</v>
+        <v>123524367</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,31 +2212,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524150</v>
+        <v>524214</v>
       </c>
       <c r="R14" t="n">
-        <v>6713800</v>
+        <v>6713917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -2812,10 +2812,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123525488</v>
+        <v>123524950</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2824,57 +2824,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524128</v>
+        <v>524192</v>
       </c>
       <c r="R19" t="n">
-        <v>6714020</v>
+        <v>6713963</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2906,7 +2892,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2916,12 +2902,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2948,10 +2929,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123524950</v>
+        <v>123525488</v>
       </c>
       <c r="B20" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2960,43 +2941,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524192</v>
+        <v>524128</v>
       </c>
       <c r="R20" t="n">
-        <v>6713963</v>
+        <v>6714020</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3028,7 +3023,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3038,7 +3033,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123310872</v>
+        <v>123311851</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,52 +823,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524248</v>
+        <v>524449</v>
       </c>
       <c r="R3" t="n">
-        <v>6713835</v>
+        <v>6713483</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123311851</v>
+        <v>123310872</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,38 +935,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524449</v>
+        <v>524248</v>
       </c>
       <c r="R4" t="n">
-        <v>6713483</v>
+        <v>6713835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,7 +1052,7 @@
         <v>123311251</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311027</v>
+        <v>123311089</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524271</v>
+        <v>524298</v>
       </c>
       <c r="R6" t="n">
-        <v>6713818</v>
+        <v>6713774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123311089</v>
+        <v>123311027</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524298</v>
+        <v>524271</v>
       </c>
       <c r="R7" t="n">
-        <v>6713774</v>
+        <v>6713818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,7 +1445,7 @@
         <v>123359713</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>123360098</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>123411453</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123524565</v>
+        <v>123523873</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,43 +1842,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524196</v>
+        <v>524302</v>
       </c>
       <c r="R11" t="n">
-        <v>6713921</v>
+        <v>6713791</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,7 +1924,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1920,7 +1934,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,10 +1966,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123523873</v>
+        <v>123524517</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>8447</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1959,57 +1978,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524302</v>
+        <v>524209</v>
       </c>
       <c r="R12" t="n">
-        <v>6713791</v>
+        <v>6713935</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2051,12 +2051,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2200,10 +2195,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524367</v>
+        <v>123524565</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2212,52 +2207,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524214</v>
+        <v>524196</v>
       </c>
       <c r="R14" t="n">
-        <v>6713917</v>
+        <v>6713921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2275,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2299,7 +2285,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2326,10 +2312,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524063</v>
+        <v>123524383</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2338,38 +2324,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524262</v>
+        <v>524223</v>
       </c>
       <c r="R15" t="n">
-        <v>6713854</v>
+        <v>6713905</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2438,10 +2438,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123524517</v>
+        <v>123524367</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2450,38 +2450,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524209</v>
+        <v>524214</v>
       </c>
       <c r="R16" t="n">
-        <v>6713935</v>
+        <v>6713917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2513,7 +2527,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2523,7 +2537,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2553,7 +2567,7 @@
         <v>123526406</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2686,10 +2700,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123524383</v>
+        <v>123524950</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2698,52 +2712,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524223</v>
+        <v>524192</v>
       </c>
       <c r="R18" t="n">
-        <v>6713905</v>
+        <v>6713963</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2775,7 +2780,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2785,7 +2790,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2812,10 +2817,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123524950</v>
+        <v>123524063</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>8447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2824,43 +2829,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524192</v>
+        <v>524262</v>
       </c>
       <c r="R19" t="n">
-        <v>6713963</v>
+        <v>6713854</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2932,7 +2932,7 @@
         <v>123525488</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3180,6 +3180,127 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124034082</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96957</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>524283</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6713661</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1049,7 +1049,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123311251</v>
+        <v>123311089</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524319</v>
+        <v>524298</v>
       </c>
       <c r="R5" t="n">
-        <v>6713759</v>
+        <v>6713774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,7 +1180,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311089</v>
+        <v>123311027</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524298</v>
+        <v>524271</v>
       </c>
       <c r="R6" t="n">
-        <v>6713774</v>
+        <v>6713818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,7 +1311,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123311027</v>
+        <v>123311251</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524271</v>
+        <v>524319</v>
       </c>
       <c r="R7" t="n">
-        <v>6713818</v>
+        <v>6713759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1830,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123523873</v>
+        <v>123526961</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,57 +1842,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524302</v>
+        <v>524165</v>
       </c>
       <c r="R11" t="n">
-        <v>6713791</v>
+        <v>6713796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1910,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1934,12 +1920,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,10 +1947,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524517</v>
+        <v>123524383</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,38 +1959,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524209</v>
+        <v>524223</v>
       </c>
       <c r="R12" t="n">
-        <v>6713935</v>
+        <v>6713905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2041,7 +2036,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2051,7 +2046,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2078,10 +2073,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123526941</v>
+        <v>123526406</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2090,31 +2085,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2123,10 +2132,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524150</v>
+        <v>524109</v>
       </c>
       <c r="R13" t="n">
-        <v>6713800</v>
+        <v>6713892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,7 +2167,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2168,7 +2177,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2312,7 +2326,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524383</v>
+        <v>123523873</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2347,7 +2361,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2360,16 +2374,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524223</v>
+        <v>524302</v>
       </c>
       <c r="R15" t="n">
-        <v>6713905</v>
+        <v>6713791</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2401,7 +2420,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2411,7 +2430,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2564,10 +2588,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123526406</v>
+        <v>123524950</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2576,57 +2600,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524109</v>
+        <v>524192</v>
       </c>
       <c r="R17" t="n">
-        <v>6713892</v>
+        <v>6713963</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2658,7 +2668,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2668,12 +2678,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2700,7 +2705,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123524950</v>
+        <v>123526941</v>
       </c>
       <c r="B18" t="n">
         <v>57507</v>
@@ -2736,19 +2741,19 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524192</v>
+        <v>524150</v>
       </c>
       <c r="R18" t="n">
-        <v>6713963</v>
+        <v>6713800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2780,7 +2785,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2790,7 +2795,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,10 +2822,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123524063</v>
+        <v>123525488</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2829,38 +2834,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524262</v>
+        <v>524128</v>
       </c>
       <c r="R19" t="n">
-        <v>6713854</v>
+        <v>6714020</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2892,7 +2916,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2902,7 +2926,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2929,10 +2958,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123525488</v>
+        <v>123524063</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2941,57 +2970,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524128</v>
+        <v>524262</v>
       </c>
       <c r="R20" t="n">
-        <v>6714020</v>
+        <v>6713854</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3023,7 +3033,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3033,12 +3043,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3065,10 +3070,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123526961</v>
+        <v>123524517</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3077,43 +3082,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524165</v>
+        <v>524209</v>
       </c>
       <c r="R21" t="n">
-        <v>6713796</v>
+        <v>6713935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311851</v>
+        <v>123311027</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +823,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524449</v>
+        <v>524271</v>
       </c>
       <c r="R3" t="n">
-        <v>6713483</v>
+        <v>6713818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +905,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +915,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1049,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123311089</v>
+        <v>123311251</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1108,10 +1127,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524298</v>
+        <v>524319</v>
       </c>
       <c r="R5" t="n">
-        <v>6713774</v>
+        <v>6713759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311027</v>
+        <v>123311089</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1215,7 +1234,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1239,10 +1258,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524271</v>
+        <v>524298</v>
       </c>
       <c r="R6" t="n">
-        <v>6713818</v>
+        <v>6713774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1293,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1303,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123311251</v>
+        <v>123311851</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,57 +1342,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524319</v>
+        <v>524449</v>
       </c>
       <c r="R7" t="n">
-        <v>6713759</v>
+        <v>6713483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1830,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123526961</v>
+        <v>123524383</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,43 +1842,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524165</v>
+        <v>524223</v>
       </c>
       <c r="R11" t="n">
-        <v>6713796</v>
+        <v>6713905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,7 +1919,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1920,7 +1929,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,7 +1956,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524383</v>
+        <v>123525488</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1982,12 +1991,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1995,16 +2004,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524223</v>
+        <v>524128</v>
       </c>
       <c r="R12" t="n">
-        <v>6713905</v>
+        <v>6714020</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2036,7 +2050,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2046,7 +2060,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2073,10 +2092,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123526406</v>
+        <v>123524565</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,57 +2104,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524109</v>
+        <v>524196</v>
       </c>
       <c r="R13" t="n">
-        <v>6713892</v>
+        <v>6713921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,7 +2172,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2177,12 +2182,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2209,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524565</v>
+        <v>123524517</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>8447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,43 +2221,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524196</v>
+        <v>524209</v>
       </c>
       <c r="R14" t="n">
-        <v>6713921</v>
+        <v>6713935</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2289,7 +2284,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2299,7 +2294,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2326,7 +2321,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123523873</v>
+        <v>123524367</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2361,7 +2356,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2374,21 +2369,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524302</v>
+        <v>524214</v>
       </c>
       <c r="R15" t="n">
-        <v>6713791</v>
+        <v>6713917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2420,7 +2410,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2430,12 +2420,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2462,7 +2447,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123524367</v>
+        <v>123526406</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2497,12 +2482,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2510,16 +2495,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524214</v>
+        <v>524109</v>
       </c>
       <c r="R16" t="n">
-        <v>6713917</v>
+        <v>6713892</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2551,7 +2541,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2561,7 +2551,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,7 +2583,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123524950</v>
+        <v>123526961</v>
       </c>
       <c r="B17" t="n">
         <v>57507</v>
@@ -2624,7 +2619,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2633,10 +2628,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524192</v>
+        <v>524165</v>
       </c>
       <c r="R17" t="n">
-        <v>6713963</v>
+        <v>6713796</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2668,7 +2663,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2678,7 +2673,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,7 +2700,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123526941</v>
+        <v>123524950</v>
       </c>
       <c r="B18" t="n">
         <v>57507</v>
@@ -2741,19 +2736,19 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524150</v>
+        <v>524192</v>
       </c>
       <c r="R18" t="n">
-        <v>6713800</v>
+        <v>6713963</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2780,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2795,7 +2790,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2822,10 +2817,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123525488</v>
+        <v>123526941</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2834,45 +2829,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2881,10 +2862,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524128</v>
+        <v>524150</v>
       </c>
       <c r="R19" t="n">
-        <v>6714020</v>
+        <v>6713800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2916,7 +2897,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2926,12 +2907,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3070,10 +3046,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123524517</v>
+        <v>123523873</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3082,38 +3058,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524209</v>
+        <v>524302</v>
       </c>
       <c r="R21" t="n">
-        <v>6713935</v>
+        <v>6713791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3145,7 +3140,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3155,7 +3150,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311027</v>
+        <v>123311089</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -846,7 +846,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524271</v>
+        <v>524298</v>
       </c>
       <c r="R3" t="n">
-        <v>6713818</v>
+        <v>6713774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,7 +942,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123310872</v>
+        <v>123311027</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -977,12 +977,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -990,16 +990,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524248</v>
+        <v>524271</v>
       </c>
       <c r="R4" t="n">
-        <v>6713835</v>
+        <v>6713818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1036,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1046,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,7 +1073,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123311251</v>
+        <v>123310872</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1103,12 +1108,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1116,21 +1121,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524319</v>
+        <v>524248</v>
       </c>
       <c r="R5" t="n">
-        <v>6713759</v>
+        <v>6713835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311089</v>
+        <v>123311251</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524298</v>
+        <v>524319</v>
       </c>
       <c r="R6" t="n">
-        <v>6713774</v>
+        <v>6713759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1830,7 +1830,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123524383</v>
+        <v>123526406</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1878,16 +1878,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524223</v>
+        <v>524109</v>
       </c>
       <c r="R11" t="n">
-        <v>6713905</v>
+        <v>6713892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1919,7 +1924,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1929,7 +1934,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1956,7 +1966,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123525488</v>
+        <v>123524383</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1991,12 +2001,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2004,21 +2014,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524128</v>
+        <v>524223</v>
       </c>
       <c r="R12" t="n">
-        <v>6714020</v>
+        <v>6713905</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2050,7 +2055,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2060,12 +2065,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2092,7 +2092,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524565</v>
+        <v>123526961</v>
       </c>
       <c r="B13" t="n">
         <v>57507</v>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524196</v>
+        <v>524165</v>
       </c>
       <c r="R13" t="n">
-        <v>6713921</v>
+        <v>6713796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2209,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524517</v>
+        <v>123524565</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,38 +2221,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524209</v>
+        <v>524196</v>
       </c>
       <c r="R14" t="n">
-        <v>6713935</v>
+        <v>6713921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2284,7 +2289,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2294,7 +2299,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2321,7 +2326,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524367</v>
+        <v>123523873</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2356,7 +2361,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2369,16 +2374,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524214</v>
+        <v>524302</v>
       </c>
       <c r="R15" t="n">
-        <v>6713917</v>
+        <v>6713791</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2410,7 +2420,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2420,7 +2430,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2447,10 +2462,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123526406</v>
+        <v>123524063</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2459,57 +2474,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524109</v>
+        <v>524262</v>
       </c>
       <c r="R16" t="n">
-        <v>6713892</v>
+        <v>6713854</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2541,7 +2537,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2551,12 +2547,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2583,10 +2574,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123526961</v>
+        <v>123525488</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2595,43 +2586,57 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524165</v>
+        <v>524128</v>
       </c>
       <c r="R17" t="n">
-        <v>6713796</v>
+        <v>6714020</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2663,7 +2668,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2673,7 +2678,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2700,10 +2710,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123524950</v>
+        <v>123524367</v>
       </c>
       <c r="B18" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2712,43 +2722,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524192</v>
+        <v>524214</v>
       </c>
       <c r="R18" t="n">
-        <v>6713963</v>
+        <v>6713917</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2780,7 +2799,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2790,7 +2809,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,10 +2836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123526941</v>
+        <v>123524517</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>8447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2829,43 +2848,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524150</v>
+        <v>524209</v>
       </c>
       <c r="R19" t="n">
-        <v>6713800</v>
+        <v>6713935</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2897,7 +2911,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2907,7 +2921,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2934,10 +2948,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123524063</v>
+        <v>123524950</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2946,38 +2960,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524262</v>
+        <v>524192</v>
       </c>
       <c r="R20" t="n">
-        <v>6713854</v>
+        <v>6713963</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3009,7 +3028,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3019,7 +3038,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3046,10 +3065,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123523873</v>
+        <v>123526941</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3058,45 +3077,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524302</v>
+        <v>524150</v>
       </c>
       <c r="R21" t="n">
-        <v>6713791</v>
+        <v>6713800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3140,7 +3145,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3150,12 +3155,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123526406</v>
+        <v>123526961</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,57 +1842,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524109</v>
+        <v>524165</v>
       </c>
       <c r="R11" t="n">
-        <v>6713892</v>
+        <v>6713796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1910,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1934,12 +1920,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,7 +1947,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524383</v>
+        <v>123526406</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -2001,12 +1982,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2014,16 +1995,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524223</v>
+        <v>524109</v>
       </c>
       <c r="R12" t="n">
-        <v>6713905</v>
+        <v>6713892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2055,7 +2041,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2065,7 +2051,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2092,10 +2083,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123526961</v>
+        <v>123524383</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2104,43 +2095,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524165</v>
+        <v>524223</v>
       </c>
       <c r="R13" t="n">
-        <v>6713796</v>
+        <v>6713905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591904</v>
+        <v>124592554</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,17 +3338,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524312</v>
+        <v>524359</v>
       </c>
       <c r="R23" t="n">
-        <v>6713764</v>
+        <v>6713627</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3434,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124592554</v>
+        <v>124591835</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3469,17 +3474,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3489,14 +3494,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524359</v>
+        <v>524313</v>
       </c>
       <c r="R24" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3528,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3538,12 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591835</v>
+        <v>124591904</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3605,7 +3610,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524313</v>
+        <v>524312</v>
       </c>
       <c r="R25" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3664,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3674,12 +3679,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124592554</v>
+        <v>124591835</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,17 +3338,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524359</v>
+        <v>524313</v>
       </c>
       <c r="R23" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591835</v>
+        <v>124591904</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524313</v>
+        <v>524312</v>
       </c>
       <c r="R24" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3543,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3575,7 +3570,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591904</v>
+        <v>124592554</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3610,17 +3605,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3630,14 +3625,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524312</v>
+        <v>524359</v>
       </c>
       <c r="R25" t="n">
-        <v>6713764</v>
+        <v>6713627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,7 +3664,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,7 +3674,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591904</v>
+        <v>124591744</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524312</v>
+        <v>524311</v>
       </c>
       <c r="R24" t="n">
-        <v>6713764</v>
+        <v>6713773</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,7 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124592554</v>
+        <v>124591904</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3605,17 +3610,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3625,14 +3630,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524359</v>
+        <v>524312</v>
       </c>
       <c r="R25" t="n">
-        <v>6713627</v>
+        <v>6713764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3664,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3674,12 +3679,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:36</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591744</v>
+        <v>124592554</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,17 +3741,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3761,14 +3761,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524311</v>
+        <v>524359</v>
       </c>
       <c r="R26" t="n">
-        <v>6713773</v>
+        <v>6713627</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591835</v>
+        <v>124591744</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524313</v>
+        <v>524311</v>
       </c>
       <c r="R23" t="n">
         <v>6713773</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591744</v>
+        <v>124592554</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524311</v>
+        <v>524359</v>
       </c>
       <c r="R24" t="n">
-        <v>6713773</v>
+        <v>6713627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3706,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124592554</v>
+        <v>124591835</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,17 +3741,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3761,14 +3761,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524359</v>
+        <v>524313</v>
       </c>
       <c r="R26" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591744</v>
+        <v>124591904</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524311</v>
+        <v>524312</v>
       </c>
       <c r="R23" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3434,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124592554</v>
+        <v>124591744</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,17 +3469,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3494,14 +3489,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524359</v>
+        <v>524311</v>
       </c>
       <c r="R24" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3528,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3538,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3575,7 +3570,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591904</v>
+        <v>124592554</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3610,17 +3605,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3630,14 +3625,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524312</v>
+        <v>524359</v>
       </c>
       <c r="R25" t="n">
-        <v>6713764</v>
+        <v>6713627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,7 +3664,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,7 +3674,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591904</v>
+        <v>124592554</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,17 +3338,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524312</v>
+        <v>524359</v>
       </c>
       <c r="R23" t="n">
-        <v>6713764</v>
+        <v>6713627</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,7 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3434,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591744</v>
+        <v>124591835</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3469,7 +3474,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3493,7 +3498,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524311</v>
+        <v>524313</v>
       </c>
       <c r="R24" t="n">
         <v>6713773</v>
@@ -3528,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3538,12 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124592554</v>
+        <v>124591744</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3605,17 +3610,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3625,14 +3630,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524359</v>
+        <v>524311</v>
       </c>
       <c r="R25" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3664,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3674,12 +3679,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,7 +3711,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591835</v>
+        <v>124591904</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,7 +3746,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3765,10 +3770,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524313</v>
+        <v>524312</v>
       </c>
       <c r="R26" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3800,7 +3805,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3815,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3575,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591744</v>
+        <v>124591904</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524311</v>
+        <v>524312</v>
       </c>
       <c r="R25" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,12 +3679,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3711,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591904</v>
+        <v>124591744</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3746,7 +3741,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3770,10 +3765,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524312</v>
+        <v>524311</v>
       </c>
       <c r="R26" t="n">
-        <v>6713764</v>
+        <v>6713773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124592554</v>
+        <v>124591744</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,17 +3338,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524359</v>
+        <v>524311</v>
       </c>
       <c r="R23" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591835</v>
+        <v>124591904</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524313</v>
+        <v>524312</v>
       </c>
       <c r="R24" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3543,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3575,7 +3570,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591904</v>
+        <v>124591835</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3610,7 +3605,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524312</v>
+        <v>524313</v>
       </c>
       <c r="R25" t="n">
-        <v>6713764</v>
+        <v>6713773</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,7 +3664,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,7 +3674,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591744</v>
+        <v>124592554</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,17 +3741,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3761,14 +3761,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524311</v>
+        <v>524359</v>
       </c>
       <c r="R26" t="n">
-        <v>6713773</v>
+        <v>6713627</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591744</v>
+        <v>124591835</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524311</v>
+        <v>524313</v>
       </c>
       <c r="R23" t="n">
         <v>6713773</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591904</v>
+        <v>124592554</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524312</v>
+        <v>524359</v>
       </c>
       <c r="R24" t="n">
-        <v>6713764</v>
+        <v>6713627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,7 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591835</v>
+        <v>124591904</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3605,7 +3610,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524313</v>
+        <v>524312</v>
       </c>
       <c r="R25" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3664,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3674,12 +3679,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124592554</v>
+        <v>124591744</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,17 +3741,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3761,14 +3761,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524359</v>
+        <v>524311</v>
       </c>
       <c r="R26" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591835</v>
+        <v>124592554</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,17 +3338,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524313</v>
+        <v>524359</v>
       </c>
       <c r="R23" t="n">
-        <v>6713773</v>
+        <v>6713627</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124592554</v>
+        <v>124591744</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524359</v>
+        <v>524311</v>
       </c>
       <c r="R24" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591904</v>
+        <v>124591835</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524312</v>
+        <v>524313</v>
       </c>
       <c r="R25" t="n">
-        <v>6713764</v>
+        <v>6713773</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,7 +3679,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,7 +3711,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591744</v>
+        <v>124591904</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,7 +3746,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3765,10 +3770,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524311</v>
+        <v>524312</v>
       </c>
       <c r="R26" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3800,7 +3805,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3815,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124592554</v>
+        <v>124591835</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,17 +3338,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524359</v>
+        <v>524313</v>
       </c>
       <c r="R23" t="n">
-        <v>6713627</v>
+        <v>6713773</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591835</v>
+        <v>124591904</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524313</v>
+        <v>524312</v>
       </c>
       <c r="R25" t="n">
-        <v>6713773</v>
+        <v>6713764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,12 +3679,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3711,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591904</v>
+        <v>124592554</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3746,17 +3741,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3766,14 +3761,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524312</v>
+        <v>524359</v>
       </c>
       <c r="R26" t="n">
-        <v>6713764</v>
+        <v>6713627</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591835</v>
+        <v>124591744</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524313</v>
+        <v>524311</v>
       </c>
       <c r="R23" t="n">
         <v>6713773</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591744</v>
+        <v>124591835</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524311</v>
+        <v>524313</v>
       </c>
       <c r="R24" t="n">
         <v>6713773</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591744</v>
+        <v>124591835</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524311</v>
+        <v>524313</v>
       </c>
       <c r="R23" t="n">
         <v>6713773</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591835</v>
+        <v>124592554</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524313</v>
+        <v>524359</v>
       </c>
       <c r="R24" t="n">
-        <v>6713773</v>
+        <v>6713627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591904</v>
+        <v>124591744</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524312</v>
+        <v>524311</v>
       </c>
       <c r="R25" t="n">
-        <v>6713764</v>
+        <v>6713773</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3679,7 +3679,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,7 +3711,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124592554</v>
+        <v>124591904</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,17 +3746,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3761,14 +3766,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524359</v>
+        <v>524312</v>
       </c>
       <c r="R26" t="n">
-        <v>6713627</v>
+        <v>6713764</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3800,7 +3805,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3815,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:36</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3303,7 +3303,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124591835</v>
+        <v>124592554</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3338,17 +3338,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524313</v>
+        <v>524359</v>
       </c>
       <c r="R23" t="n">
-        <v>6713773</v>
+        <v>6713627</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124592554</v>
+        <v>124591904</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524359</v>
+        <v>524312</v>
       </c>
       <c r="R24" t="n">
-        <v>6713627</v>
+        <v>6713764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,12 +3543,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:36</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3711,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591904</v>
+        <v>124591835</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3746,7 +3741,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3770,10 +3765,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524312</v>
+        <v>524313</v>
       </c>
       <c r="R26" t="n">
-        <v>6713764</v>
+        <v>6713773</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3570,7 +3570,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591744</v>
+        <v>124591835</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524311</v>
+        <v>524313</v>
       </c>
       <c r="R25" t="n">
         <v>6713773</v>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,7 +3706,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591835</v>
+        <v>124591744</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524313</v>
+        <v>524311</v>
       </c>
       <c r="R26" t="n">
         <v>6713773</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4712,6 +4712,127 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127727522</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>524245</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6713763</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4833,6 +4833,234 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128218294</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>524305</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6713475</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128218164</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92668</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>524288</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6713500</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4717,7 +4717,7 @@
         <v>127727522</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128218164</v>
       </c>
       <c r="B36" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>126936747</v>
       </c>
       <c r="B27" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>126964224</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>126964244</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>126962144</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126963963</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126963918</v>
       </c>
       <c r="B32" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>126964000</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5061,6 +5061,239 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131852153</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>524213</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6713730</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131851767</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>524422</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6713518</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -5066,7 +5066,7 @@
         <v>131852153</v>
       </c>
       <c r="B37" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>131851767</v>
       </c>
       <c r="B38" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -5178,7 +5178,7 @@
         <v>131851767</v>
       </c>
       <c r="B38" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122915193</v>
+        <v>123311851</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524288</v>
+        <v>524449</v>
       </c>
       <c r="R2" t="n">
-        <v>6713811</v>
+        <v>6713483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Under en äldre gran, 2 överblommade från förra året.</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,69 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123311089</v>
+        <v>123524565</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524298</v>
+        <v>524196</v>
       </c>
       <c r="R3" t="n">
-        <v>6713774</v>
+        <v>6713921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,22 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,69 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123311027</v>
+        <v>123524950</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524271</v>
+        <v>524192</v>
       </c>
       <c r="R4" t="n">
-        <v>6713818</v>
+        <v>6713963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,22 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,52 +1006,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123310872</v>
+        <v>123526941</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1127,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524248</v>
+        <v>524150</v>
       </c>
       <c r="R5" t="n">
-        <v>6713835</v>
+        <v>6713800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,22 +1076,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,69 +1118,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123311251</v>
+        <v>123526961</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524319</v>
+        <v>524165</v>
       </c>
       <c r="R6" t="n">
-        <v>6713759</v>
+        <v>6713796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,53 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123311851</v>
+        <v>131843634</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524449</v>
+        <v>524145</v>
       </c>
       <c r="R7" t="n">
-        <v>6713483</v>
+        <v>6713721</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,22 +1300,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,67 +1342,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123360098</v>
+        <v>131852153</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524214</v>
+        <v>524213</v>
       </c>
       <c r="R8" t="n">
-        <v>6713889</v>
+        <v>6713730</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1526,22 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,15 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123359713</v>
+        <v>134372375</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,48 +1465,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524277</v>
+        <v>524230</v>
       </c>
       <c r="R9" t="n">
-        <v>6713805</v>
+        <v>6713751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1652,22 +1533,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,72 +1575,62 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123411453</v>
+        <v>131851248</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524217</v>
+        <v>524416</v>
       </c>
       <c r="R10" t="n">
-        <v>6713890</v>
+        <v>6713441</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1783,27 +1654,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>10-20 bladrosetter.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1830,32 +1696,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123526961</v>
+        <v>134372167</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103023</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1866,7 +1727,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1875,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524165</v>
+        <v>524266</v>
       </c>
       <c r="R11" t="n">
-        <v>6713796</v>
+        <v>6713775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1905,22 +1766,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,32 +1808,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123526941</v>
+        <v>134372414</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1983,19 +1839,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524150</v>
+        <v>524201</v>
       </c>
       <c r="R12" t="n">
-        <v>6713800</v>
+        <v>6713748</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2022,22 +1878,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2064,55 +1920,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524565</v>
+        <v>123524063</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524196</v>
+        <v>524262</v>
       </c>
       <c r="R13" t="n">
-        <v>6713921</v>
+        <v>6713854</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2144,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2154,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2181,69 +2027,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123523873</v>
+        <v>123524517</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524302</v>
+        <v>524209</v>
       </c>
       <c r="R14" t="n">
-        <v>6713791</v>
+        <v>6713935</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2275,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2285,12 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2317,15 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524517</v>
+        <v>128218294</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,16 +2163,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524209</v>
+        <v>524305</v>
       </c>
       <c r="R15" t="n">
-        <v>6713935</v>
+        <v>6713475</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2387,22 +2204,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,15 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123526406</v>
+        <v>122915193</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2464,12 +2276,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2488,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524109</v>
+        <v>524288</v>
       </c>
       <c r="R16" t="n">
-        <v>6713892</v>
+        <v>6713811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2518,27 +2330,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>Under en äldre gran, 2 överblommade från förra året.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2565,50 +2377,64 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123524063</v>
+        <v>122916997</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524262</v>
+        <v>524142</v>
       </c>
       <c r="R17" t="n">
-        <v>6713854</v>
+        <v>6713729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2635,22 +2461,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2677,15 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123525488</v>
+        <v>122917069</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2712,7 +2538,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2732,14 +2558,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524128</v>
+        <v>524154</v>
       </c>
       <c r="R18" t="n">
-        <v>6714020</v>
+        <v>6713729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2766,22 +2592,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2813,55 +2639,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123524950</v>
+        <v>122957710</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524192</v>
+        <v>524145</v>
       </c>
       <c r="R19" t="n">
-        <v>6713963</v>
+        <v>6713733</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2888,22 +2718,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2930,15 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123524383</v>
+        <v>122958064</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2965,12 +2795,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2978,16 +2808,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524223</v>
+        <v>524144</v>
       </c>
       <c r="R20" t="n">
-        <v>6713905</v>
+        <v>6713722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3014,22 +2849,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3056,15 +2896,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123524367</v>
+        <v>122958244</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3091,12 +2926,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3104,16 +2939,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524214</v>
+        <v>524143</v>
       </c>
       <c r="R21" t="n">
-        <v>6713917</v>
+        <v>6713721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3140,22 +2980,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3182,59 +3027,64 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124034082</v>
+        <v>122958484</v>
       </c>
       <c r="B22" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524283</v>
+        <v>524142</v>
       </c>
       <c r="R22" t="n">
-        <v>6713661</v>
+        <v>6713723</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3261,22 +3111,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3303,15 +3153,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124592554</v>
+        <v>122958550</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3338,17 +3183,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3358,14 +3203,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524359</v>
+        <v>524147</v>
       </c>
       <c r="R23" t="n">
-        <v>6713627</v>
+        <v>6713728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3392,27 +3237,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,15 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124591904</v>
+        <v>122958631</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3474,12 +3314,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3494,14 +3334,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524312</v>
+        <v>524136</v>
       </c>
       <c r="R24" t="n">
-        <v>6713764</v>
+        <v>6713723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3528,22 +3368,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,15 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124591835</v>
+        <v>123310872</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3605,12 +3445,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3618,21 +3458,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524313</v>
+        <v>524248</v>
       </c>
       <c r="R25" t="n">
-        <v>6713773</v>
+        <v>6713835</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3659,27 +3494,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Inom ca 3 kv/dm.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3706,15 +3536,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124591744</v>
+        <v>123311027</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3741,12 +3566,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3765,10 +3590,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524311</v>
+        <v>524271</v>
       </c>
       <c r="R26" t="n">
-        <v>6713773</v>
+        <v>6713818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3795,27 +3620,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På en yta av ca 0.5kv/dm.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3842,10 +3662,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126936747</v>
+        <v>123311089</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3872,17 +3692,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3891,10 +3716,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524288</v>
+        <v>524298</v>
       </c>
       <c r="R27" t="n">
-        <v>6713820</v>
+        <v>6713774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3921,22 +3746,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3963,10 +3788,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126964224</v>
+        <v>123311251</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3993,17 +3818,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4017,10 +3842,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524279</v>
+        <v>524319</v>
       </c>
       <c r="R28" t="n">
-        <v>6713844</v>
+        <v>6713759</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4047,22 +3872,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4089,10 +3914,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126964244</v>
+        <v>123359713</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4119,22 +3944,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4143,10 +3963,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524280</v>
+        <v>524277</v>
       </c>
       <c r="R29" t="n">
-        <v>6713844</v>
+        <v>6713805</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4173,22 +3993,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4215,10 +4035,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126962144</v>
+        <v>123360098</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4245,17 +4065,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4264,10 +4084,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524099</v>
+        <v>524214</v>
       </c>
       <c r="R30" t="n">
-        <v>6713924</v>
+        <v>6713889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4294,22 +4114,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4336,10 +4156,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126963963</v>
+        <v>123411453</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4366,17 +4186,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4390,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524305</v>
+        <v>524217</v>
       </c>
       <c r="R31" t="n">
-        <v>6713787</v>
+        <v>6713890</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4420,22 +4240,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>10-20 bladrosetter.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4462,10 +4287,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126963918</v>
+        <v>123523873</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4492,17 +4317,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4516,10 +4341,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524298</v>
+        <v>524302</v>
       </c>
       <c r="R32" t="n">
-        <v>6713794</v>
+        <v>6713791</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4546,22 +4371,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 15 bladrosetter inom ca 3 kv/dm. Under 2 klena granar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4588,10 +4418,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126964000</v>
+        <v>123524367</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4618,22 +4448,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4642,10 +4467,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524330</v>
+        <v>524214</v>
       </c>
       <c r="R33" t="n">
-        <v>6713764</v>
+        <v>6713917</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4657,7 +4482,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4667,27 +4492,27 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4714,10 +4539,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727522</v>
+        <v>123524383</v>
       </c>
       <c r="B34" t="n">
-        <v>98490</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4744,17 +4569,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4763,10 +4588,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524245</v>
+        <v>524223</v>
       </c>
       <c r="R34" t="n">
-        <v>6713763</v>
+        <v>6713905</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4793,22 +4618,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4835,50 +4660,64 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128218294</v>
+        <v>123525488</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524305</v>
+        <v>524128</v>
       </c>
       <c r="R35" t="n">
-        <v>6713475</v>
+        <v>6714020</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4905,22 +4744,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4947,54 +4791,64 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128218164</v>
+        <v>123526406</v>
       </c>
       <c r="B36" t="n">
-        <v>92812</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524288</v>
+        <v>524109</v>
       </c>
       <c r="R36" t="n">
-        <v>6713500</v>
+        <v>6713892</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5021,22 +4875,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5063,53 +4922,67 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131852153</v>
+        <v>123526470</v>
       </c>
       <c r="B37" t="n">
-        <v>57946</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524213</v>
+        <v>524101</v>
       </c>
       <c r="R37" t="n">
-        <v>6713730</v>
+        <v>6713880</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5133,22 +5006,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5175,10 +5048,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131851767</v>
+        <v>124432412</v>
       </c>
       <c r="B38" t="n">
-        <v>99106</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5205,7 +5078,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5224,13 +5097,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524422</v>
+        <v>524183</v>
       </c>
       <c r="R38" t="n">
-        <v>6713518</v>
+        <v>6713449</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5254,22 +5127,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5296,59 +5169,64 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134372375</v>
+        <v>124591744</v>
       </c>
       <c r="B39" t="n">
-        <v>57796</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524230</v>
+        <v>524311</v>
       </c>
       <c r="R39" t="n">
-        <v>6713751</v>
+        <v>6713773</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5375,22 +5253,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På en yta av ca 0.5kv/dm.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5417,50 +5300,64 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134372414</v>
+        <v>124591835</v>
       </c>
       <c r="B40" t="n">
-        <v>58658</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524201</v>
+        <v>524313</v>
       </c>
       <c r="R40" t="n">
-        <v>6713748</v>
+        <v>6713773</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5487,22 +5384,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Inom ca 3 kv/dm.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5526,6 +5428,2103 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124591904</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>524312</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6713764</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124592554</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>524359</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6713627</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom 3 kv/dm.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126932450</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>524097</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6713893</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126932846</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>524149</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6713719</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126936299</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>524172</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6713431</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126936747</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>524288</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6713820</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126962144</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>524099</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6713924</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126963918</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>524298</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6713794</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126963963</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>524305</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6713787</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126964000</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>524330</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6713764</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126964224</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>524279</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6713844</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126964244</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>524280</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6713844</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127727522</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>524245</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6713763</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129114973</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>524137</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6713729</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131851232</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>524414</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6713448</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett 20tal bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131851767</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>524422</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6713518</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>124034082</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>524283</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6713661</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36739-2024 artfynd.xlsx
+++ b/artfynd/A 36739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123311851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524565</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526941</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526961</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131843634</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131852153</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134372375</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851248</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134372167</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134372414</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524063</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524517</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2243,6 +2313,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128218294</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2374,6 +2449,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915193</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2505,6 +2585,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916997</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2636,6 +2721,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122917069</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2762,6 +2852,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122957710</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2893,6 +2988,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958064</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3024,6 +3124,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958244</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3150,6 +3255,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958484</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3281,6 +3391,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958550</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3412,6 +3527,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958631</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3533,6 +3653,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123310872</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3659,6 +3784,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123311027</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3785,6 +3915,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123311089</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3911,6 +4046,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123311251</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4032,6 +4172,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359713</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4153,6 +4298,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123360098</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4284,6 +4434,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123411453</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4415,6 +4570,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123523873</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4536,6 +4696,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524367</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4657,6 +4822,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524383</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4788,6 +4958,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525488</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4919,6 +5094,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526406</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5045,6 +5225,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526470</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5166,6 +5351,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432412</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5297,6 +5487,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124591744</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5428,6 +5623,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124591835</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5554,6 +5754,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124591904</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5685,6 +5890,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124592554</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5806,6 +6016,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932450</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5927,6 +6142,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932846</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6048,6 +6268,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936299</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6169,6 +6394,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936747</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6290,6 +6520,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962144</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6416,6 +6651,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963918</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6542,6 +6782,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963963</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6668,6 +6913,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126964000</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6794,6 +7044,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126964224</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6920,6 +7175,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126964244</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7041,6 +7301,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127727522</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7162,6 +7427,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114973</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7288,6 +7558,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851232</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7409,6 +7684,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851767</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7525,8 +7805,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124034082</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>